--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0.2pF</t>
+          <t>0.6pF</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>GJM0335C1ER20WB01D</t>
+          <t>GJM0335C1ER60WB01D</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr"/>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>115R</t>
+          <t>56R</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>RC0201FR-07115RL</t>
+          <t>RC0201FR-0756RL</t>
         </is>
       </c>
       <c r="H30" s="6" t="inlineStr"/>

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
@@ -3951,12 +3951,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>INA241A3IDGKRDGK0008A-MFG</t>
+          <t>INA241A4IDGKRDGK0008A-MFG</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>INA241A3IDGKRDGK0008A-MFG</t>
+          <t>INA241A4IDGKRDGK0008A-MFG</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>INA241A3IDGKR</t>
+          <t>INA241A4IDGKR</t>
         </is>
       </c>
       <c r="H93" s="6" t="inlineStr"/>

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I104"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="4.140625" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3684,76 +3684,73 @@
     </row>
     <row r="86" ht="20.1" customHeight="1" s="3">
       <c r="A86" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BPF2</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BPF2</t>
+          <t>LED-BLUE0603</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BPF2</t>
+          <t>LED-0603</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>U$2, U$3</t>
+          <t>D2, D3, D4, D5</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Blue SMD LED</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Not a component</t>
-        </is>
-      </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>[DNP不要贴];</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>Do not put</t>
-        </is>
-      </c>
+          <t>KB EELP41.12-P1R2-36-3X4X-5-R18</t>
+        </is>
+      </c>
+      <c r="H86" s="6" t="inlineStr"/>
+      <c r="I86" s="5" t="inlineStr"/>
     </row>
     <row r="87" ht="20.1" customHeight="1" s="3">
       <c r="A87" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>CJT-T-P-HH-ST-TH1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LED-BLUE0603</t>
+          <t>CJT-T-P-HH-ST-TH1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LED-0603</t>
+          <t>CJTTPHHSTTH1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>D2, D3, D4, D5</t>
+          <t>J19, J21</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blue SMD LED</t>
+          <t>Conn Twinax F 0Hz to 4GHz 100Ohm Solder ST Thru-Hole Gold</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>KB EELP41.12-P1R2-36-3X4X-5-R18</t>
+          <t>CJT-T-P-HH-ST-TH1</t>
         </is>
       </c>
       <c r="H87" s="6" t="inlineStr"/>
@@ -3765,32 +3762,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CJT-T-P-HH-ST-TH1</t>
+          <t>DAC5578SRGET</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CJT-T-P-HH-ST-TH1</t>
+          <t>DAC5578SRGET</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>CJTTPHHSTTH1</t>
+          <t>RGE24_2P7X2P7</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>J19, J21</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Conn Twinax F 0Hz to 4GHz 100Ohm Solder ST Thru-Hole Gold</t>
+          <t>U7, U69</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>CJT-T-P-HH-ST-TH1</t>
+          <t>DAC5578SRGET</t>
         </is>
       </c>
       <c r="H88" s="6" t="inlineStr"/>
@@ -3798,35 +3790,48 @@
     </row>
     <row r="89" ht="20.1" customHeight="1" s="3">
       <c r="A89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>DAC5578SRGET</t>
+          <t>ECS-120-10-36B2-JTN-TR</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DAC5578SRGET</t>
+          <t>CRYSTAL-12MHZ</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>RGE24_2P7X2P7</t>
+          <t>CRYSTAL-SMD-2X2.5MM</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>U7, U69</t>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>12.0MHz Crystal</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>DAC5578SRGET</t>
-        </is>
-      </c>
-      <c r="H89" s="6" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr"/>
+          <t>ECS-120-10-36B2-JTN-TR</t>
+        </is>
+      </c>
+      <c r="H89" s="6" t="inlineStr">
+        <is>
+          <t>The correct package for the listed Part Number [ECS-120-10-36B2-JTN-TR] is indeed [SMD2520-4P], not [CRYSTAL-12MHZ『 』CRYSTAL-SMD-2X2.5MM].Please confirm.</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>Okay, Please proceed</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="20.1" customHeight="1" s="3">
       <c r="A90" t="n">
@@ -3834,44 +3839,31 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ECS-120-10-36B2-JTN-TR</t>
+          <t>EP4RKU+</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CRYSTAL-12MHZ</t>
+          <t>EP4RKU+</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>CRYSTAL-SMD-2X2.5MM</t>
+          <t>DG1677-2_MNC</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>12.0MHz Crystal</t>
+          <t>U16</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>ECS-120-10-36B2-JTN-TR</t>
-        </is>
-      </c>
-      <c r="H90" s="6" t="inlineStr">
-        <is>
-          <t>The correct package for the listed Part Number [ECS-120-10-36B2-JTN-TR] is indeed [SMD2520-4P], not [CRYSTAL-12MHZ『 』CRYSTAL-SMD-2X2.5MM].Please confirm.</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>Okay, Please proceed</t>
-        </is>
-      </c>
+          <t>EP4RKU+</t>
+        </is>
+      </c>
+      <c r="H90" s="6" t="inlineStr"/>
+      <c r="I90" s="5" t="inlineStr"/>
     </row>
     <row r="91" ht="20.1" customHeight="1" s="3">
       <c r="A91" t="n">
@@ -3879,171 +3871,176 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EP4RKU+</t>
+          <t>FT2232HQ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>EP4RKU+</t>
+          <t>FT2232HQ</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DG1677-2_MNC</t>
+          <t>64QFN_FT2232HQ_FTD</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>U16</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>EP4RKU+</t>
-        </is>
-      </c>
-      <c r="H91" s="6" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr"/>
+          <t>FT2232HQ</t>
+        </is>
+      </c>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>The part we can get here was made in the year of 2022+ OK？</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>Okay, Please proceed</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="20.1" customHeight="1" s="3">
       <c r="A92" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FT2232HQ</t>
+          <t>INA241A4IDGKRDGK0008A-MFG</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FT2232HQ</t>
+          <t>INA241A4IDGKRDGK0008A-MFG</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>64QFN_FT2232HQ_FTD</t>
+          <t>DGK0008A-MFG</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U11, U73, U74, U75, U76, U77, U78, U79, U80, U81, U82, U83, U84, U85, U86, U87</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>FT2232HQ</t>
-        </is>
-      </c>
-      <c r="H92" s="6" t="inlineStr">
-        <is>
-          <t>The part we can get here was made in the year of 2022+ OK？</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>Okay, Please proceed</t>
-        </is>
-      </c>
+          <t>INA241A4IDGKR</t>
+        </is>
+      </c>
+      <c r="H92" s="6" t="inlineStr"/>
+      <c r="I92" s="5" t="inlineStr"/>
     </row>
     <row r="93" ht="20.1" customHeight="1" s="3">
       <c r="A93" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>INA241A4IDGKRDGK0008A-MFG</t>
+          <t>LTC5552IUDBTRMPBF</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>INA241A4IDGKRDGK0008A-MFG</t>
+          <t>LTC5552IUDBTRMPBF</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>DGK0008A-MFG</t>
+          <t>UDB_12_ADI</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>U11, U73, U74, U75, U76, U77, U78, U79, U80, U81, U82, U83, U84, U85, U86, U87</t>
+          <t>U5, U13</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>INA241A4IDGKR</t>
-        </is>
-      </c>
-      <c r="H93" s="6" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr"/>
+          <t>LTC5552IUDB#TRMPBF</t>
+        </is>
+      </c>
+      <c r="H93" s="6" t="inlineStr">
+        <is>
+          <t>[Price is changing higher, final price should be subjected to the real price when order!]</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Okay, Please proceed</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="20.1" customHeight="1" s="3">
       <c r="A94" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LTC5552IUDBTRMPBF</t>
+          <t>M3SWA2-34DR+</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LTC5552IUDBTRMPBF</t>
+          <t>M3SWA2-34DR+</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>UDB_12_ADI</t>
+          <t>16_QFN</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>U5, U13</t>
+          <t>RF_SW_1, RF_SW_2, RF_SW_3, RF_SW_4, RF_SW_5, RF_SW_6, RF_SW_7, RF_SW_8, RF_SW_9, RF_SW_10, RF_SW_11, RF_SW_12, RF_SW_13, RF_SW_14, RF_SW_15, RF_SW_16, U$1</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>LTC5552IUDB#TRMPBF</t>
-        </is>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>[Price is changing higher, final price should be subjected to the real price when order!]</t>
-        </is>
-      </c>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>Okay, Please proceed</t>
-        </is>
-      </c>
+          <t>M3SWA2-34DR+</t>
+        </is>
+      </c>
+      <c r="H94" s="6" t="inlineStr"/>
+      <c r="I94" s="5" t="inlineStr"/>
     </row>
     <row r="95" ht="20.1" customHeight="1" s="3">
       <c r="A95" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>M3SWA2-34DR+</t>
+          <t>MINI-USB-32005-201</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>M3SWA2-34DR+</t>
+          <t>MINI-USB-32005-201</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>16_QFN</t>
+          <t>32005-201</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RF_SW_1, RF_SW_2, RF_SW_3, RF_SW_4, RF_SW_5, RF_SW_6, RF_SW_7, RF_SW_8, RF_SW_9, RF_SW_10, RF_SW_11, RF_SW_12, RF_SW_13, RF_SW_14, RF_SW_15, RF_SW_16, U$1</t>
+          <t>X2, X53</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>MINI USB-B Conector</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>M3SWA2-34DR+</t>
+          <t>10118192-0002LF</t>
         </is>
       </c>
       <c r="H95" s="6" t="inlineStr"/>
@@ -4051,36 +4048,36 @@
     </row>
     <row r="96" ht="20.1" customHeight="1" s="3">
       <c r="A96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MINI-USB-32005-201</t>
+          <t>MOMENTARY-SWITCH-SPST-SMD-4.6X2.8MM</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MINI-USB-32005-201</t>
+          <t>MOMENTARY-SWITCH-SPST-SMD-4.6X2.8MM</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>32005-201</t>
+          <t>TACTILE_SWITCH_SMD_4.6X2.8MM</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>X2, X53</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>MINI USB-B Conector</t>
+          <t>Momentary Switch (Pushbutton) - SPST</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>10118192-0002LF</t>
+          <t>EVQP0E07K</t>
         </is>
       </c>
       <c r="H96" s="6" t="inlineStr"/>
@@ -4092,32 +4089,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>MOMENTARY-SWITCH-SPST-SMD-4.6X2.8MM</t>
+          <t>MT25QL01GBBB8E12-0AUT</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MOMENTARY-SWITCH-SPST-SMD-4.6X2.8MM</t>
+          <t>MT25QL01GBBB8E12-0AUT</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TACTILE_SWITCH_SMD_4.6X2.8MM</t>
+          <t>BGA24_MT25QL_MRN</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>S1</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Momentary Switch (Pushbutton) - SPST</t>
+          <t>U9</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>EVQP0E07K</t>
+          <t>MT25QL01GBBB8E12-0AUT</t>
         </is>
       </c>
       <c r="H97" s="6" t="inlineStr"/>
@@ -4129,31 +4121,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>MT25QL01GBBB8E12-0AUT</t>
+          <t>NX3215SA-32.768KHz</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MT25QL01GBBB8E12-0AUT</t>
+          <t>NX3225GD-8MHZ-STD-CRA-3</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>BGA24_MT25QL_MRN</t>
+          <t>XTAL_NX3225GD-8MHZ-STD-CRA-3_N</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>U9</t>
+          <t>XTAL3</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>MT25QL01GBBB8E12-0AUT</t>
-        </is>
-      </c>
-      <c r="H98" s="6" t="inlineStr"/>
-      <c r="I98" s="5" t="inlineStr"/>
+          <t>NX3215SA-32.768K-STD-MUS-2</t>
+        </is>
+      </c>
+      <c r="H98" s="6" t="inlineStr">
+        <is>
+          <t>The quoted part number is [NX3215SA-32.768K-STD-MUS-2], not [NX3225GD-8MHZ-STD-CRA-3/XTAL] as specified in description</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>Okay, Please proceed</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="20.1" customHeight="1" s="3">
       <c r="A99" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>NX3215SA-32.768KHz</t>
+          <t>NX3225GD-8MHZ-STD-CRA-3</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4176,17 +4176,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>XTAL3</t>
+          <t>XTAL1</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>NX3215SA-32.768K-STD-MUS-2</t>
+          <t>NX3225GD-8MHZ-STD-CRA-3</t>
         </is>
       </c>
       <c r="H99" s="6" t="inlineStr">
         <is>
-          <t>The quoted part number is [NX3215SA-32.768K-STD-MUS-2], not [NX3225GD-8MHZ-STD-CRA-3/XTAL] as specified in description</t>
+          <t>The quoted part number is [NX3225GD-8MHZ-STD-CRA-3], not [XTAL] as specified in description,The correct package for the listed Part Number [NX3225GD-8MHZ-STD-CRA-3] is indeed [SMD3225-2P], not [3225].Please confirm.</t>
         </is>
       </c>
       <c r="I99" s="5" t="inlineStr">
@@ -4197,190 +4197,235 @@
     </row>
     <row r="100" ht="20.1" customHeight="1" s="3">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NX3225GD-8MHZ-STD-CRA-3</t>
+          <t>OPA4703EA/250</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NX3225GD-8MHZ-STD-CRA-3</t>
+          <t>OPA4703EA/250</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>XTAL_NX3225GD-8MHZ-STD-CRA-3_N</t>
+          <t>PW14</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>XTAL1</t>
+          <t>OPA_1, OPA_2, OPA_3, OPA_4</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>NX3225GD-8MHZ-STD-CRA-3</t>
-        </is>
-      </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>The quoted part number is [NX3225GD-8MHZ-STD-CRA-3], not [XTAL] as specified in description,The correct package for the listed Part Number [NX3225GD-8MHZ-STD-CRA-3] is indeed [SMD3225-2P], not [3225].Please confirm.</t>
-        </is>
-      </c>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>Okay, Please proceed</t>
-        </is>
-      </c>
+          <t>OPA4703EA/250</t>
+        </is>
+      </c>
+      <c r="H100" s="6" t="inlineStr"/>
+      <c r="I100" s="5" t="inlineStr"/>
     </row>
     <row r="101" ht="20.1" customHeight="1" s="3">
       <c r="A101" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>OPA4703EA/250</t>
+          <t>STM32F746ZGT7</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>OPA4703EA/250</t>
+          <t>STM32F746ZGT7</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>PW14</t>
+          <t>LQFP-144_STM</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OPA_1, OPA_2, OPA_3, OPA_4</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>OPA4703EA/250</t>
-        </is>
-      </c>
-      <c r="H101" s="6" t="inlineStr"/>
-      <c r="I101" s="5" t="inlineStr"/>
+          <t>STM32F746ZGT7</t>
+        </is>
+      </c>
+      <c r="H101" s="6" t="inlineStr">
+        <is>
+          <t>The part we can get here was made in the year of 2022+ OK？</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>Okay, Please proceed</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="20.1" customHeight="1" s="3">
       <c r="A102" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>STM32F746ZGT7</t>
+          <t>SZMMSZ5232BT1G</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>STM32F746ZGT7</t>
+          <t>SZMMSZ5232BT1G</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LQFP-144_STM</t>
+          <t>SOD-123_ONS</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U14, U15, U17, U37, U38, U39, U40, U41, U43, U44, U45, U46, U47, U48, U49, U50, U51, U52, U53, U54, U55, U56, U57, U58, U59, U60, U61, U62, U63, U64, U65, U66, U67, U68</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>STM32F746ZGT7</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="inlineStr">
-        <is>
-          <t>The part we can get here was made in the year of 2022+ OK？</t>
-        </is>
-      </c>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>Okay, Please proceed</t>
-        </is>
-      </c>
+          <t>SZMMSZ5232BT1G</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr"/>
+      <c r="I102" s="5" t="inlineStr"/>
     </row>
     <row r="103" ht="20.1" customHeight="1" s="3">
       <c r="A103" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SZMMSZ5232BT1G</t>
+          <t>XC7A50T-2FTG256I</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SZMMSZ5232BT1G</t>
+          <t>XC7A50T-2FTG256I</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SOD-123_ONS</t>
+          <t>BGA256C100P16X16_1700X1700X155</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>U14, U15, U17, U37, U38, U39, U40, U41, U43, U44, U45, U46, U47, U48, U49, U50, U51, U52, U53, U54, U55, U56, U57, U58, U59, U60, U61, U62, U63, U64, U65, U66, U67, U68</t>
+          <t>U42</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Artix-7 Field Programmable Gate Array (FPGA) IC 170 2764800 52160 256-LBGA  Check availability</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>SZMMSZ5232BT1G</t>
-        </is>
-      </c>
-      <c r="H103" s="6" t="inlineStr"/>
-      <c r="I103" s="5" t="inlineStr"/>
+          <t>XC7A50T-2FTG256I</t>
+        </is>
+      </c>
+      <c r="H103" s="6" t="inlineStr">
+        <is>
+          <t>information on chip will be removed</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>Okay, Please proceed</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="20.1" customHeight="1" s="3">
       <c r="A104" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>XC7A50T-2FTG256I</t>
+          <t>142-0731-211</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>XC7A50T-2FTG256I</t>
+          <t>142-0731-211</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>BGA256C100P16X16_1700X1700X155</t>
+          <t>1420731211</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>U42</t>
+          <t>J56, J57, J58, J59</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Artix-7 Field Programmable Gate Array (FPGA) IC 170 2764800 52160 256-LBGA  Check availability</t>
-        </is>
-      </c>
-      <c r="G104" s="5" t="inlineStr">
-        <is>
-          <t>XC7A50T-2FTG256I</t>
-        </is>
-      </c>
-      <c r="H104" s="6" t="inlineStr">
-        <is>
-          <t>information on chip will be removed</t>
-        </is>
-      </c>
-      <c r="I104" s="5" t="inlineStr">
-        <is>
-          <t>Okay, Please proceed</t>
+          <t>SMA jack female, 50 ohm, through-hole (cavity filter launches)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>142-0731-211</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>B1.3: one pair per TX/RX filter path</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0R</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>RR0201</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>R0201</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>R174, R175</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>RESISTOR, European symbol</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>RCA02010000ZSEDSR</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>bench bypass</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>DNP in production: fit only when the cavity filters are not fitted</t>
         </is>
       </c>
     </row>

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I105"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="4.140625" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -912,7 +912,7 @@
     </row>
     <row r="13" ht="20.1" customHeight="1" s="3">
       <c r="A13" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>C1, C2, C4, C5, C6, C7, C8, C9, C10, C11, C12, C13, C14, C15, C16, C36, C37, C38, C39, C40, C41, C42, C44, C45, C46, C47, C51, C52, C53, C56, C67, C69, C74, C80, C82, C125, C131, C133, C138, C140, C146, C148, C159, C160, C162, C168, C170, C175, C188, C189, C190, C192, C193, C194, C195, C196, C201, C203, C208, C210, C215, C217, C222, C224, C229, C231, C236, C238, C243, C245, C250, C252, C293</t>
+          <t>C1, C2, C4, C5, C6, C7, C8, C9, C10, C11, C12, C13, C14, C15, C16, C36, C37, C38, C39, C40, C41, C42, C44, C45, C46, C47, C51, C52, C53, C56, C67, C69, C74, C80, C82, C125, C131, C133, C138, C140, C146, C148, C159, C160, C162, C168, C170, C175, C188, C189, C190, C192, C193, C194, C195, C196, C201, C203, C208, C210, C215, C217, C222, C224, C229, C231, C236, C238, C243, C245, C250, C252, C293, C354, C355, C356, C357, C358, C359</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1458,7 +1458,7 @@
     </row>
     <row r="27" ht="20.1" customHeight="1" s="3">
       <c r="A27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>R39, R40, R83, R84, R111, R123, R145, R151, R153</t>
+          <t>R39, R40, R83, R84, R111, R123, R145, R151, R153, R176, R177</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2315,7 +2315,7 @@
     </row>
     <row r="50" ht="20.1" customHeight="1" s="3">
       <c r="A50" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>X1, X4, X5, X6, X7, X8, X9, X10, X11, X12, X13, X14, X15, X16, X17, X18, X19, X20, X21, X22, X24, X54, X55, X56, X_1, X_2, X_3, X_4, X_5, X_6, X_7, X_8, X_9, X_10, X_11, X_12, X_13, X_14, X_15, X_16</t>
+          <t>X1, X4, X5, X6, X7, X8, X9, X10, X11, X12, X13, X14, X15, X16, X17, X18, X19, X20, X21, X22, X24, X54, X55, X56, X_1, X_2, X_3, X_4, X_5, X_6, X_7, X_8, X_9, X_10, X_11, X_12, X_13, X_14, X_15, X_16, X57</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4426,6 +4426,86 @@
       <c r="I105" t="inlineStr">
         <is>
           <t>DNP in production: fit only when the cavity filters are not fitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TXS0104EPWR</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TXS0104EPWR</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>PW0014A-MFG</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>U90</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>VOLTAGE LEVEL TRANSLATOR</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>TXS0104EPWR</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Lane B B1.1: level-shifts the QSPI lines so bank 14 can run at 2.5 V</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TXS0102DCUR</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>TXS0102DCUR</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>DCU0008A-MFG</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>U91</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>VOLTAGE LEVEL TRANSLATOR</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>TXS0102DCUR</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Lane B B1.1: level-shifts the QSPI lines so bank 14 can run at 2.5 V</t>
         </is>
       </c>
     </row>

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
@@ -1458,7 +1458,7 @@
     </row>
     <row r="27" ht="20.1" customHeight="1" s="3">
       <c r="A27" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>R39, R40, R83, R84, R111, R123, R145, R151, R153, R176, R177</t>
+          <t>R39, R40, R83, R84, R111, R123, R145, R151, R153, R176, R177, R178, R179, R180, R181, R182, R183, R184, R185, R186, R187, R188, R189, R190, R191, R192, R193, R178, R179, R180, R181, R182, R183, R184, R185, R186, R187, R188, R189, R190, R191, R192, R193</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I107"/>
+  <dimension ref="A1:I108"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col width="4.140625" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2315,7 +2315,7 @@
     </row>
     <row r="50" ht="20.1" customHeight="1" s="3">
       <c r="A50" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>X1, X4, X5, X6, X7, X8, X9, X10, X11, X12, X13, X14, X15, X16, X17, X18, X19, X20, X21, X22, X24, X54, X55, X56, X_1, X_2, X_3, X_4, X_5, X_6, X_7, X_8, X_9, X_10, X_11, X_12, X_13, X_14, X_15, X_16, X57</t>
+          <t>X1, X4, X8, X9, X10, X12, X16, X17, X18, X20, X21, X24, X25, X26, X27, X54, X55, X56, X57, X_1, X_2, X_3, X_4, X_5, X_6, X_7, X_8, X_9, X_10, X_11, X_12, X_13, X_14, X_15, X_16</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2352,7 +2352,7 @@
     </row>
     <row r="51" ht="20.1" customHeight="1" s="3">
       <c r="A51" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>X3, X38, X39, X40, X41, X42, X43, X44, X45, X46, X47, X48, X49, X50, X51, X52</t>
+          <t>X3, X6, X11, X13, X15, X19, X22, X38, X39, X40, X41, X42, X43, X44, X45, X46, X47, X48, X49, X50, X51, X52</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4506,6 +4506,41 @@
       <c r="I107" t="inlineStr">
         <is>
           <t>Lane B B1.1: level-shifts the QSPI lines so bank 14 can run at 2.5 V</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>3</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>22-23-2041</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>22-23-2021</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>22-23-2041</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>X5, X7, X14</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>.100 (2.54mm) Center Header - 2 Pin"</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>22-23-2041</t>
         </is>
       </c>
     </row>

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
@@ -1458,7 +1458,7 @@
     </row>
     <row r="27" ht="20.1" customHeight="1" s="3">
       <c r="A27" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>R39, R40, R83, R84, R111, R123, R145, R151, R153, R176, R177, R178, R179, R180, R181, R182, R183, R184, R185, R186, R187, R188, R189, R190, R191, R192, R193, R178, R179, R180, R181, R182, R183, R184, R185, R186, R187, R188, R189, R190, R191, R192, R193</t>
+          <t>R39, R40, R83, R84, R111, R123, R145, R151, R153, R176, R177, R178, R179, R180, R181, R182, R183, R184, R185, R186, R187, R188, R189, R190, R191, R192, R193, R178, R179, R180, R181, R182, R183, R184, R185, R186, R187, R188, R189, R190, R191, R192, R193, R194</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2841,7 +2841,7 @@
     </row>
     <row r="64" ht="20.1" customHeight="1" s="3">
       <c r="A64" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>R42, R44, R45, R46, R47, R48, R50, R52, R53, R54, R65, R66, R67, R68, R69, R70, R71, R72, R73, R74, R75, R76, R77, R117, R141, R142, R143</t>
+          <t>R42, R44, R45, R46, R47, R48, R50, R52, R53, R54, R65, R66, R67, R68, R69, R70, R71, R72, R73, R74, R75, R76, R77, R117, R141, R142, R143, R195</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4431,7 +4431,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>U90</t>
+          <t>U90, U92</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
@@ -1458,7 +1458,7 @@
     </row>
     <row r="27" ht="20.1" customHeight="1" s="3">
       <c r="A27" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>R39, R40, R83, R84, R111, R123, R145, R151, R153, R176, R177, R178, R179, R180, R181, R182, R183, R184, R185, R186, R187, R188, R189, R190, R191, R192, R193, R178, R179, R180, R181, R182, R183, R184, R185, R186, R187, R188, R189, R190, R191, R192, R193, R194</t>
+          <t>R39, R40, R83, R84, R111, R123, R145, R151, R153, R176, R177, R178, R179, R180, R181, R182, R183, R184, R185, R186, R187, R188, R189, R190, R191, R192, R193, R194, R196, R197, R198, R199, R200, R201, R202, R203</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1490,7 +1490,11 @@
           <t>AC0201FR-0710KL</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>R196-R203 added for the eight temperature channels (#5); duplicate designators removed (44 listed -&gt; 36 unique)</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="inlineStr"/>
     </row>
     <row r="28" ht="20.1" customHeight="1" s="3">

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2.443k</t>
+          <t>2.43k</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2163,10 +2163,14 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>RC0201FR-072K44L</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr"/>
+          <t>RC0201FR-072K43L</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>E96 correction: 2.443k was not an E96 value; 2.43k is</t>
+        </is>
+      </c>
       <c r="I45" s="5" t="inlineStr"/>
     </row>
     <row r="46" ht="20.1" customHeight="1" s="3">
@@ -2738,7 +2742,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3k2</t>
+          <t>3.16k</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2763,10 +2767,14 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>RC0201FR-073K2L</t>
-        </is>
-      </c>
-      <c r="H61" s="6" t="inlineStr"/>
+          <t>RC0201FR-073K16L</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>E96 correction: 3.2k is not E96; 3.16k is (equidistant with 3.24k)</t>
+        </is>
+      </c>
       <c r="I61" s="5" t="inlineStr"/>
     </row>
     <row r="62" ht="20.1" customHeight="1" s="3">
@@ -3090,7 +3098,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>500R</t>
+          <t>499R</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3115,10 +3123,14 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>RC0201FR-07500RL</t>
-        </is>
-      </c>
-      <c r="H70" s="6" t="inlineStr"/>
+          <t>RC0201FR-07499RL</t>
+        </is>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
+        <is>
+          <t>E96 correction: 500R is E24; 499R is the E96 value</t>
+        </is>
+      </c>
       <c r="I70" s="5" t="inlineStr"/>
     </row>
     <row r="71" ht="20.1" customHeight="1" s="3">
@@ -3320,7 +3332,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>830R</t>
+          <t>825R</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3345,10 +3357,14 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>RC0402FR-07830RL</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="inlineStr"/>
+          <t>RC0402FR-07825RL</t>
+        </is>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>E96 correction: 830R is not E96; 825R is the nearer one</t>
+        </is>
+      </c>
       <c r="I76" s="5" t="inlineStr"/>
     </row>
     <row r="77" ht="20.1" customHeight="1" s="3">
@@ -3357,7 +3373,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>840R</t>
+          <t>845R</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3382,10 +3398,14 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>RC0201FR-07840RL</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="inlineStr"/>
+          <t>RC0201FR-07845RL</t>
+        </is>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
+          <t>E96 correction: 840R is not E96; 845R is the nearer one</t>
+        </is>
+      </c>
       <c r="I77" s="5" t="inlineStr"/>
     </row>
     <row r="78" ht="20.1" customHeight="1" s="3">

--- a/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
+++ b/4_Schematics and Boards Layout/4_7_Production Files/Gerber_Main_Board/BOM_Main_Board.xlsx
@@ -2919,12 +2919,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>GRM033R71E472KA88D</t>
+          <t>GRM033R71E472KE14J</t>
         </is>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>The part we will supply is 	GRM033R61A472KA01D  OK？</t>
+          <t>The part we will supply is 	GRM033R61A472KA01D  OK？; MPN corrected: the KA88 suffix does not exist; KE14 is the real 4.7nF 25V X7R 0201, 195 in stock at DigiKey. No footprint change (0201)</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>GRM033R60J475ME47D</t>
+          <t>GRM033R60J475ME05D</t>
         </is>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>The part we will supply is 	GRM035R60J475ME15D OK？</t>
+          <t>The part we will supply is 	GRM035R60J475ME15D OK？; MPN corrected: the ME47 suffix does not exist; ME05 is the real 4.7uF 6.3V X5R 0201. No footprint change (0201)</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>GRM033R71E473KA88D</t>
+          <t>GRM033R61A473ME84D</t>
         </is>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>The part we will supply is 	GRM033R61C473KE84D OK？</t>
+          <t>The part we will supply is 	GRM033R61C473KE84D OK？; MPN corrected: no 47nF 25V part exists in GRM033; 10V 47nF X5R 0201 is stocked (14,131) and the part sits on +3V3, so 10V is ample. No footprint change (0201)</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
